--- a/docs/basic-design.xlsx
+++ b/docs/basic-design.xlsx
@@ -203,7 +203,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">バックエンド: Go (Gin) / フロントエンド: Next.js (React) — 2026-08-27 決定</t>
+          <t xml:space="preserve">バックエンド: Go (Gin + GORM) / フロントエンド: Next.js (React) — 2026-08-27 決定</t>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">テーブル定義書 (./table-definition.md) / README (../README.md)</t>
+          <t xml:space="preserve">実装手順書 (./implementation-guide.md) / Go の書き方入門 (./go-guide.md) / テーブル定義書 (./table-definition.md) / README (../README.md)</t>
         </is>
       </c>
     </row>
@@ -264,7 +264,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">技術スタックは バックエンド Go (Gin) + フロントエンド Next.js (React) を採用する (2026-08-27 決定)。以降の設計はこの組み合わせを前提に記述する。</t>
+          <t xml:space="preserve">技術スタックは バックエンド Go (Gin + GORM) + フロントエンド Next.js (React) を採用する (2026-08-27 決定)。以降の設計はこの組み合わせを前提に記述する。</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">API サーバ (Go + Gin)</t>
+          <t xml:space="preserve">API サーバ (Go + Gin + GORM)</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go 1.x + Gin + database/sql (webapp/go)</t>
+          <t xml:space="preserve">Go 1.22 + Gin v1.10 + GORM v1.31 (webapp/go)</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MySQL ドライバは go-sql-driver/mysql</t>
+          <t xml:space="preserve">ドライバは gorm.io/driver/mysql</t>
         </is>
       </c>
     </row>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SQL の発行。employee / area / duty の3つ</t>
+          <t xml:space="preserve">GORM を使った DB アクセス。employee / area / duty の3つ</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">型定義</t>
+          <t xml:space="preserve">モデル / 型定義</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Employee / Area / Duty</t>
+          <t xml:space="preserve">GORM モデル (Employee / Area / Duty) と API 応答用の DutyView</t>
         </is>
       </c>
     </row>
@@ -2412,155 +2412,162 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・さらに internal/db が 2秒間隔で最大30回 (最長60秒) の接続リトライを行い、初回起動時の DB 初期化待ちを吸収する。</t>
+          <t xml:space="preserve">・さらに internal/db が 2秒間隔で最大30回 (最長60秒) の接続リトライを行い、初回起動時の DB 初期化待ちを吸収する</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">(gorm.Open 後に *sql.DB を取り出して Ping している)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">・nginx は webapp / frontend に依存する (起動順のみ、healthy 待ちはしない)。</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5.3 文字コード</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">DB・接続文字列とも utf8mb4 に統一する。日本語データの文字化けを防ぐため、以下をすべて揃えている。</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">・MySQL サーバ起動オプション: --character-set-server=utf8mb4 / --collation-server=utf8mb4_unicode_ci / --skip-character-set-client-handshake</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・初期化 SQL 冒頭: SET NAMES utf8mb4;</t>
+          <t xml:space="preserve">・MySQL サーバ起動オプション: --character-set-server=utf8mb4 / --collation-server=utf8mb4_unicode_ci / --skip-character-set-client-handshake</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・接続 DSN: charset=utf8mb4&amp;parseTime=true&amp;loc=Local</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+          <t xml:space="preserve">・初期化 SQL 冒頭: SET NAMES utf8mb4;</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・接続 DSN: charset=utf8mb4&amp;parseTime=true&amp;loc=Local (GORM の gorm.io/driver/mysql に渡す)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5.4 性能・可用性</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">プロトタイプのため冗長化・スケールアウトは考慮しない。データ量は社員30名・当番が週25件増加する規模を想定し、duties には scheduled_date と employee_id のインデックスを用意している。</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5.5 セキュリティ</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">項目</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">現状</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">認証・認可</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">なし。API・画面とも誰でもアクセスできる</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">通信の暗号化</t>
+          <t xml:space="preserve">認証・認可</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">なし (HTTP)。ローカル開発前提</t>
+          <t xml:space="preserve">なし。API・画面とも誰でもアクセスできる</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">資格情報</t>
+          <t xml:space="preserve">通信の暗号化</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DB のユーザ/パスワードは compose ファイルに平文で記述</t>
+          <t xml:space="preserve">なし (HTTP)。ローカル開発前提</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DB ポート</t>
+          <t xml:space="preserve">資格情報</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3306 をホストに公開している</t>
+          <t xml:space="preserve">DB のユーザ/パスワードは compose ファイルに平文で記述</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">DB ポート</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3306 をホストに公開している</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">SQL インジェクション</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">すべての SQL でプレースホルダ (?) を使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GORM のパラメータバインドを使用。Where("id = ?", id) のように値は必ず ? で渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">本番運用にはそのまま適さない。社内公開する場合は認証の追加、資格情報の外部化、3306 / 8081 の非公開化が前提となる。</t>
         </is>

--- a/docs/basic-design.xlsx
+++ b/docs/basic-design.xlsx
@@ -215,7 +215,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装手順書 (./implementation-guide.md) / Go の書き方入門 (./go-guide.md) / テーブル定義書 (./table-definition.md) / README (../README.md)</t>
+          <t xml:space="preserve">API 仕様書 (./api-spec.md) / 実装手順書 (./implementation-guide.md) / Go の書き方入門 (./go-guide.md) / テーブル定義書 (./table-definition.md) / README (../README.md)</t>
         </is>
       </c>
     </row>
@@ -1569,511 +1569,475 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・ベース URL: http://localhost:8080/api</t>
+          <t xml:space="preserve">本節は設計判断の記録である。リクエスト/レスポンスの詳細な仕様は API 仕様書 (./api-spec.md) を一次情報とする</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・リクエスト / レスポンスとも application/json (UTF-8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">・認証: なし</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">(エラー形式、ステータスコードの使い分け、未確定事項、検討中の API も同文書にまとめている)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">・ベース URL: http://localhost:8080/api</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・リクエスト / レスポンスとも application/json (UTF-8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・認証: なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">・日付は YYYY-MM-DD 形式の文字列</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 GET /api/health</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">死活確認。DB への Ping / SELECT 1 を実行する。</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ステータス</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ボディ</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9">
+    <row r="16">
+      <c r="A16" s="9">
         <v>200</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"status": "ok"}</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9">
+    <row r="17">
+      <c r="A17" s="9">
         <v>500</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"status": "ng", "error": "&lt;エラーメッセージ&gt;"}</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 GET /api/employees</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">社員一覧を id 昇順で返す (active による絞り込みは行わない)。</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  { "id": 1, "name": "佐藤 一郎", "email": "sato.ichiro@example.com", "department": "営業部", "active": true }</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">]</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">フィールド</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">型</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">社員ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氏名</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">email</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">department</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">部署名</t>
+          <t xml:space="preserve">社員ID</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氏名</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メールアドレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部署名</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">boolean</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">在籍フラグ</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー時は 500 / {"error": "..."}。</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.3 GET /api/areas</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">掃除エリア一覧を id 昇順で返す。</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">[</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  { "id": 1, "name": "会議室A", "description": "机・椅子の整頓、ホワイトボード消去" }</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">]</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">フィールド</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">型</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">id</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">number</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">エリアID</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">string</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">エリア名</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">description</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">string</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">作業内容</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー時は 500 / {"error": "..."}。</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.4 GET /api/duties</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">当番一覧を scheduled_date 昇順 → areas.id 昇順で返す。社員名・エリア名を JOIN 済みで含むため、フロントは追加の問い合わせを行わない。期間絞り込みのパラメータは持たず、常に全件を返す。</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  {</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "id": 1,</t>
-        </is>
-      </c>
-    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "employee_id": 1,</t>
+          <t xml:space="preserve">[</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "employee_name": "佐藤 一郎",</t>
+          <t xml:space="preserve">  {</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "area_id": 1,</t>
+          <t xml:space="preserve">    "id": 1,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "area_name": "会議室A",</t>
+          <t xml:space="preserve">    "employee_id": 1,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "scheduled_date": "2026-08-27",</t>
+          <t xml:space="preserve">    "employee_name": "佐藤 一郎",</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "status": "pending"</t>
+          <t xml:space="preserve">    "area_id": 1,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t xml:space="preserve">    "area_name": "会議室A",</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">    "scheduled_date": "2026-08-27",</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "status": "pending"</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">]</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">フィールド</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">型</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当番ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">employee_id</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当社員ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">employee_name</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当社員の氏名</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">area_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
@@ -2083,31 +2047,31 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">エリアID</t>
+          <t xml:space="preserve">当番ID</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">area_name</t>
+          <t xml:space="preserve">employee_id</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">エリア名</t>
+          <t xml:space="preserve">担当社員ID</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">scheduled_date</t>
+          <t xml:space="preserve">employee_name</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -2117,117 +2081,168 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">実施予定日 (YYYY-MM-DD)</t>
+          <t xml:space="preserve">担当社員の氏名</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">area_id</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エリアID</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">area_name</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">エリア名</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheduled_date</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実施予定日 (YYYY-MM-DD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">string</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pending / done / swapped</t>
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">エラー時は 500 / {"error": "..."}。</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.5 POST /api/duties/generate</t>
         </is>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">翌週分の当番を生成する。リクエストボディなし。</t>
         </is>
       </c>
     </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ステータス</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ボディ</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">発生条件</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9">
+    <row r="83">
+      <c r="A83" s="9">
         <v>200</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"created": 25}</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">正常終了。created は登録件数</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9">
+    <row r="84">
+      <c r="A84" s="9">
         <v>400</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"error": "employees or areas is empty"}</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">有効な社員またはエリアが0件</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9">
+    <row r="85">
+      <c r="A85" s="9">
         <v>500</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">{"error": "..."}</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DB エラー等</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">参考実装の FastAPI (Python) では、400 のボディが FastAPI の既定形式 {"detail": "..."} になる。参考実装に切り替えて動作確認する場合は注意する。</t>
         </is>

--- a/docs/basic-design.xlsx
+++ b/docs/basic-design.xlsx
@@ -256,7 +256,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">社員マスタと掃除エリアマスタをもとに、翌週5日分の掃除当番をランダムに抽選・登録し、一覧表示する Web アプリケーション。</t>
+          <t xml:space="preserve">社員 (person) と掃除タスク (task) をもとに、翌週5日分の掃除当番をランダムに抽選・登録し、一覧表示する Web アプリケーション。</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GORM を使った DB アクセス。employee / area / duty の3つ</t>
+          <t xml:space="preserve">GORM を使った DB アクセス。person / task / lottery_result に対応</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GORM モデル (Employee / Area / Duty) と API 応答用の DutyView</t>
+          <t xml:space="preserve">GORM モデル (Employee / Area / Duty) と API 応答用の DutyView。Area は task の互換APIモデル</t>
         </is>
       </c>
     </row>
@@ -1368,21 +1368,21 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・employees から active = 1 の社員 ID を全件取得する。</t>
+          <t xml:space="preserve">・person から active = 1 の社員 ID を全件取得する。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・areas から全エリア ID を取得する。</t>
+          <t xml:space="preserve">・task から全掃除タスク ID を取得する。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・いずれかが空の場合はエラー (employees or areas is empty) とし、HTTP 400 を返す。</t>
+          <t xml:space="preserve">・いずれかが空の場合はエラー (person or task is empty) とし、HTTP 400 を返す。</t>
         </is>
       </c>
     </row>

--- a/docs/basic-design.xlsx
+++ b/docs/basic-design.xlsx
@@ -1197,7 +1197,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET /api/employees</t>
+          <t xml:space="preserve">GET /api/people</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">エリア一覧参照</t>
+          <t xml:space="preserve">掃除タスク一覧参照</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">全掃除エリアを ID 順に取得</t>
+          <t xml:space="preserve">全掃除タスクを ID 順に取得</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET /api/areas</t>
+          <t xml:space="preserve">GET /api/tasks</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">当番一覧参照</t>
+          <t xml:space="preserve">抽選結果一覧参照</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">当番を社員名・エリア名込みで日付順に取得</t>
+          <t xml:space="preserve">抽選結果を社員名・掃除タスク名込みで日付順に取得</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GET /api/duties</t>
+          <t xml:space="preserve">GET /api/lottery-results</t>
         </is>
       </c>
     </row>
@@ -1334,17 +1334,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">当番生成</t>
+          <t xml:space="preserve">抽選結果生成</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">翌週5日分 × 全エリアの当番をランダム抽選で登録</t>
+          <t xml:space="preserve">翌週5日分 × 全掃除タスクの抽選結果を登録</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POST /api/duties/generate</t>
+          <t xml:space="preserve">POST /api/lottery-results/generate</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">押下で POST /api/duties/generate を実行。処理中は disabled、完了時に生成件数をダイアログ表示し一覧を再取得</t>
+          <t xml:space="preserve">押下で POST /api/lottery-results/generate を実行。処理中は disabled、完了時に生成件数をダイアログ表示し一覧を再取得</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">初期表示時に GET /api/employees と GET /api/duties を並列で呼び出す。API は相対パス (/api/...) で呼ぶため、環境ごとのエンドポイント設定を持たない。</t>
+          <t xml:space="preserve">初期表示時に GET /api/people と GET /api/lottery-results を並列で呼び出す。API は相対パス (/api/...) で呼ぶため、環境ごとのエンドポイント設定を持たない。</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 GET /api/employees</t>
+          <t xml:space="preserve">4.2 GET /api/people</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 GET /api/areas</t>
+          <t xml:space="preserve">4.3 GET /api/tasks</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 GET /api/duties</t>
+          <t xml:space="preserve">4.4 GET /api/lottery-results</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 POST /api/duties/generate</t>
+          <t xml:space="preserve">4.5 POST /api/lottery-results/generate</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">当番状態の更新 API (pending → done)</t>
+          <t xml:space="preserve">抽選結果状態の更新 API (pending → done)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">duties.status。PATCH /api/duties/:id を追加</t>
+          <t xml:space="preserve">lottery_result.status。PATCH /api/lottery-results/:id を追加</t>
         </is>
       </c>
     </row>
